--- a/results_all_thermostat.xlsx
+++ b/results_all_thermostat.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
           <t>Claude Judgment Reasoning</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Claude Confidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +528,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +572,11 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,6 +616,11 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,6 +660,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -683,6 +708,11 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -722,6 +752,11 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -761,6 +796,11 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,6 +840,11 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -839,6 +884,11 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +928,11 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -917,6 +972,11 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -956,6 +1016,11 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -995,6 +1060,11 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1034,6 +1104,11 @@
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1073,6 +1148,11 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1116,6 +1196,11 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1159,6 +1244,11 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1202,6 +1292,11 @@
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1245,6 +1340,11 @@
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1288,6 +1388,11 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1331,6 +1436,11 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1373,9 +1483,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Lizzie=Maybe: The keyword "cerberus" matched the Android game title "Seisen Cerberus" — this is a mobile game app, not an embedded home device. Fails all 3 definition criteria. Clear false positive.</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1421,6 +1532,11 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1459,9 +1575,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Lizzie=Maybe: The word "thermostat" in the product name matched the keyword, but Red Hat Thermostat is a JVM monitoring tool (CPE: thermostat_project:thermostat). Not an embedded device, not deployed in a home. Fails all 3 definition criteria.</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1507,6 +1624,11 @@
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1550,6 +1672,11 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1593,6 +1720,11 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1636,6 +1768,11 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1679,6 +1816,11 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1722,6 +1864,11 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1764,9 +1911,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Lizzie=Maybe: Honeywell model numbers CT60/CN80/CT40 triggered the thermostat keyword match on "CT", but these are enterprise industrial handheld barcode scanners. CPE strings confirm Honeywell mobile computers, not thermostats. Fails criterion 1 (residential deployment).</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1812,6 +1960,11 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1855,6 +2008,11 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1898,6 +2056,11 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1941,6 +2104,11 @@
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1984,6 +2152,11 @@
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2027,6 +2200,11 @@
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2070,6 +2248,11 @@
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2113,6 +2296,11 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2157,7 +2345,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Lizzie=Maybe: Siemens Cerberus DMS is a building document management/fire alarm system; Desigo CC is a commercial building automation platform. Both are enterprise-grade systems used in commercial buildings. Fails criterion 1 (residential, without dedicated security oversight).</t>
+          <t>Siemens Cerberus DMS and Desigo CC are enterprise building management/fire alarm platforms used in commercial buildings, not residential homes. Fails criterion 1 — not a residential deployment without dedicated security oversight.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2203,6 +2396,11 @@
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2246,6 +2444,11 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2289,6 +2492,11 @@
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2332,6 +2540,11 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2376,7 +2589,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Lizzie=Maybe: Siemens Cerberus DMS and WinCC OA are industrial SCADA/building automation platforms, not home IoT. Same reasoning as CVE-2021-37181. Fails criterion 1 (residential deployment without dedicated security oversight).</t>
+          <t>Siemens Cerberus DMS and WinCC OA are industrial SCADA/building automation platforms. Same reasoning as CVE-2021-37181 — fails criterion 1 (residential deployment without dedicated security oversight).</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2421,9 +2639,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Lizzie=Maybe: Meross is a consumer smart home brand sold through major retail channels. The MSH30Q is their smart home thermostat — description explicitly references thermostat temperature control. CPE confirms the hardware. Meets all 3 definition criteria, upgrading from Maybe to Yes.</t>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2469,6 +2688,11 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2514,6 +2738,11 @@
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2557,6 +2786,11 @@
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2596,6 +2830,11 @@
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2639,6 +2878,11 @@
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2683,6 +2927,11 @@
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2722,6 +2971,11 @@
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2761,6 +3015,11 @@
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2806,7 +3065,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Lizzie=Yes: Siemens Cerberus PRO EN is a professional-grade commercial fire detection system (fire panels, engineering tools, cloud distribution). Primarily deployed in commercial buildings and public infrastructure, not typical home IoT. CPE confirms enterprise product line. Downgraded to Maybe rather than No because residential fire panels do exist.</t>
+          <t>Siemens Cerberus PRO EN is a professional fire detection system primarily deployed in commercial buildings. Residential fire panels do exist but this is an enterprise-grade product line. CPE confirms Siemens commercial product — not typical home IoT.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2850,7 +3114,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Lizzie=Yes: Same as CVE-2024-22039 — Siemens Cerberus PRO commercial fire safety system. No CPE string available, making device context harder to confirm. Downgraded to Maybe.</t>
+          <t>Same as CVE-2024-22039 — Siemens Cerberus PRO EN commercial fire detection system. No CPE string available to further confirm device context.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2894,7 +3163,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Lizzie=Yes: Same as CVE-2024-22039 — Siemens Cerberus PRO commercial fire safety system. No CPE string available. Downgraded to Maybe.</t>
+          <t>Same as CVE-2024-22039 — Siemens Cerberus PRO EN commercial fire detection system. No CPE string available.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2940,6 +3214,11 @@
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2979,6 +3258,11 @@
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3017,9 +3301,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Upgraded from Maybe to Yes: description explicitly names an embedded web server on a thermostat accessible via LAN and home router port forwarding — unambiguous home IoT content. Missing CPE is likely a NIST data lag on a 2025 CVE, not evidence of ambiguity. Spirit of criterion 3 is satisfied by the description itself.</t>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3065,6 +3350,11 @@
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results_all_thermostat.xlsx
+++ b/results_all_thermostat.xlsx
@@ -468,17 +468,17 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Claude Judgment</t>
+          <t>AI Judgment</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Claude Judgment Reasoning</t>
+          <t>AI Judgment Reasoning</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Claude Confidence</t>
+          <t>AI Confidence</t>
         </is>
       </c>
     </row>
